--- a/backend/data/financials_by_company/1663.HK.xlsx
+++ b/backend/data/financials_by_company/1663.HK.xlsx
@@ -4014,7 +4014,7 @@
         <v>-369000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0.012039997</v>
